--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -7,10 +7,11 @@
     <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="全部数据" sheetId="1" r:id="rId1"/>
     <sheet name="主框架消融" sheetId="2" r:id="rId2"/>
     <sheet name="自适应模块消融" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="训练时间" sheetId="5" r:id="rId4"/>
+    <sheet name="训练迭代数" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="49">
   <si>
     <t>主干框架的消融</t>
   </si>
@@ -97,7 +98,7 @@
     <t>F</t>
   </si>
   <si>
-    <t>---</t>
+    <t>(F=0)</t>
   </si>
   <si>
     <t>myLog</t>
@@ -320,7 +321,56 @@
     <t>FF(RS)</t>
   </si>
   <si>
-    <t>Q10</t>
+    <r>
+      <t>Q10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.25"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.25"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Q11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>79.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.25"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.25"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
   <si>
     <r>
@@ -410,7 +460,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,6 +522,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.25"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -614,6 +670,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.25"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -977,137 +1039,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1138,35 +1200,44 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1479,95 +1550,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="11.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="14.212962962963" customWidth="1"/>
     <col min="7" max="7" width="11.462962962963" customWidth="1"/>
     <col min="8" max="9" width="10.5185185185185" customWidth="1"/>
-    <col min="10" max="10" width="22.9259259259259" customWidth="1"/>
-    <col min="11" max="11" width="29" customWidth="1"/>
+    <col min="10" max="10" width="20.5740740740741" customWidth="1"/>
+    <col min="11" max="11" width="27.0648148148148" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.15" customHeight="1" spans="1:11">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:11">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" ht="15.15" spans="1:11">
-      <c r="A3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="A3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1578,31 +1649,31 @@
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:11">
-      <c r="A4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="A4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="16">
         <v>0.5</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1613,31 +1684,31 @@
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:11">
-      <c r="A5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="A5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="16">
         <v>0.5</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1648,31 +1719,31 @@
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:11">
-      <c r="A6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="A6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="16">
         <v>0.5</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="6" t="s">
@@ -1683,31 +1754,31 @@
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:11">
-      <c r="A7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="A7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="16">
         <v>0.5</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -1718,31 +1789,31 @@
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:11">
-      <c r="A8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="A8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="16">
         <v>0.5</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -1753,31 +1824,31 @@
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:11">
-      <c r="A9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="A9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="16">
         <v>0.5</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -1788,31 +1859,31 @@
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:11">
-      <c r="A10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="14" t="s">
+      <c r="A10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="17">
         <v>0.1</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="6" t="s">
@@ -1823,31 +1894,31 @@
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:11">
-      <c r="A11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="14" t="s">
+      <c r="A11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="21">
         <v>1</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -1858,31 +1929,31 @@
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:11">
-      <c r="A12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="A12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="16">
         <v>0.5</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="16" t="s">
         <v>29</v>
       </c>
       <c r="J12" s="6" t="s">
@@ -1892,32 +1963,32 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="13" ht="15.15" spans="1:11">
-      <c r="A13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="14" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="16" t="s">
         <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
@@ -1928,31 +1999,31 @@
       </c>
     </row>
     <row r="14" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="14" t="s">
+      <c r="A14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="21">
         <v>1</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="16" t="s">
         <v>29</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -1963,38 +2034,73 @@
       </c>
     </row>
     <row r="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="14" t="s">
+      <c r="A15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="21">
         <v>1</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="16" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="6">
-        <v>79.4</v>
+      <c r="K15" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" s="10" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="21">
+        <v>1</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2183,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G3" s="6">
         <v>0.727</v>
@@ -2100,7 +2206,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G4" s="6">
         <v>0.789</v>
@@ -2123,13 +2229,13 @@
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6">
         <v>0.787</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="15.15"/>
@@ -2186,10 +2292,10 @@
         <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:8">
@@ -2209,10 +2315,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" ht="15.15" spans="1:8">
@@ -2232,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" s="6">
         <v>0.795</v>
@@ -2316,7 +2422,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G3" s="6">
         <v>0.778</v>
@@ -2339,7 +2445,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" s="6">
         <v>0.779</v>
@@ -2362,7 +2468,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6">
         <v>0.787</v>
@@ -2422,10 +2528,10 @@
         <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:7">
@@ -2445,10 +2551,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" ht="15.15" spans="1:7">
@@ -2468,7 +2574,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" s="6">
         <v>0.795</v>
@@ -2502,4 +2608,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="50">
   <si>
     <t>主干框架的消融</t>
   </si>
@@ -327,7 +327,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color theme="0" tint="-0.25"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -336,7 +335,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color theme="0" tint="-0.25"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
@@ -350,7 +348,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color theme="0" tint="-0.25"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -359,11 +356,10 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color theme="0" tint="-0.25"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>?</t>
+      <t>79.5</t>
     </r>
   </si>
   <si>
@@ -371,6 +367,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>R1</t>
   </si>
   <si>
     <r>
@@ -460,7 +459,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,8 +515,35 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -673,7 +699,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color theme="0" tint="-0.25"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1039,137 +1064,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1200,6 +1225,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1221,22 +1249,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1550,7 +1596,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="11.1666666666667" customWidth="1"/>
@@ -1562,153 +1608,153 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.15" customHeight="1" spans="1:11">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:11">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" ht="15.15" spans="1:11">
-      <c r="A3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="A3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="21">
         <v>72.7</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:11">
-      <c r="A4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="16" t="s">
+    <row r="4" s="10" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="23">
         <v>0.5</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="24">
         <v>78.9</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:11">
-      <c r="A5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="A5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="17">
         <v>0.5</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1719,31 +1765,31 @@
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:11">
-      <c r="A6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="A6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="17">
         <v>0.5</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="6" t="s">
@@ -1754,31 +1800,31 @@
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:11">
-      <c r="A7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="16" t="s">
+      <c r="A7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="17">
         <v>0.5</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -1804,16 +1850,16 @@
       <c r="E8" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="F8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="17">
         <v>0.5</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -1839,16 +1885,16 @@
       <c r="E9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="F9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="17">
         <v>0.5</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -1874,16 +1920,16 @@
       <c r="E10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="16" t="s">
+      <c r="F10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="18">
         <v>0.1</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="6" t="s">
@@ -1909,16 +1955,16 @@
       <c r="E11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="16" t="s">
+      <c r="F11" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="27">
         <v>1</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -1944,16 +1990,16 @@
       <c r="E12" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="F12" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="17">
         <v>0.5</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="17" t="s">
         <v>29</v>
       </c>
       <c r="J12" s="6" t="s">
@@ -1963,7 +2009,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" ht="15.15" spans="1:11">
       <c r="A13" s="19" t="s">
         <v>14</v>
       </c>
@@ -1979,16 +2025,16 @@
       <c r="E13" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="16" t="s">
+      <c r="F13" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="17" t="s">
         <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
@@ -2014,16 +2060,16 @@
       <c r="E14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="16" t="s">
+      <c r="F14" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="27">
         <v>1</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="17" t="s">
         <v>29</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2049,58 +2095,93 @@
       <c r="E15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="16" t="s">
+      <c r="F15" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="27">
         <v>1</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" s="10" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="16" t="s">
+    <row r="16" s="11" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="27">
         <v>1</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="29" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="17" s="11" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="27">
+        <v>1</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="6">
+        <v>78.3</v>
       </c>
     </row>
   </sheetData>
@@ -2183,7 +2264,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" s="6">
         <v>0.727</v>
@@ -2206,7 +2287,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="6">
         <v>0.789</v>
@@ -2229,13 +2310,13 @@
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="6">
         <v>0.787</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="15.15"/>
@@ -2292,10 +2373,10 @@
         <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:8">
@@ -2315,10 +2396,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="15.15" spans="1:8">
@@ -2338,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="6">
         <v>0.795</v>
@@ -2422,7 +2503,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="6">
         <v>0.778</v>
@@ -2445,7 +2526,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="6">
         <v>0.779</v>
@@ -2468,7 +2549,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="6">
         <v>0.787</v>
@@ -2528,10 +2609,10 @@
         <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:7">
@@ -2551,10 +2632,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="15.15" spans="1:7">
@@ -2574,7 +2655,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="6">
         <v>0.795</v>

--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500"/>
+    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="全部数据" sheetId="1" r:id="rId1"/>
     <sheet name="主框架消融" sheetId="2" r:id="rId2"/>
     <sheet name="自适应模块消融" sheetId="3" r:id="rId3"/>
-    <sheet name="训练时间" sheetId="5" r:id="rId4"/>
-    <sheet name="训练迭代数" sheetId="4" r:id="rId5"/>
+    <sheet name="训练迭代数" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="64">
   <si>
     <t>主干框架的消融</t>
   </si>
@@ -285,6 +284,9 @@
     </r>
   </si>
   <si>
+    <t>√√</t>
+  </si>
+  <si>
     <t>Q</t>
   </si>
   <si>
@@ -322,6 +324,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Q10</t>
     </r>
     <r>
@@ -343,6 +350,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>79.4</t>
     </r>
     <r>
@@ -366,10 +378,10 @@
     <t>R</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
   </si>
   <si>
     <r>
@@ -436,16 +448,55 @@
     <t>软体真的有效吗？（这里显示软体是一个负面效果）</t>
   </si>
   <si>
+    <t>刚体运动</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
     <t>？</t>
   </si>
   <si>
-    <t>1I2-CATH</t>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R5</t>
   </si>
   <si>
     <t>2G-CATH</t>
   </si>
   <si>
     <t>1H-CATH</t>
+  </si>
+  <si>
+    <t>训练时间</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>RTX 2080 Ti x2</t>
+  </si>
+  <si>
+    <t>迭代次量</t>
+  </si>
+  <si>
+    <t>×0.25</t>
+  </si>
+  <si>
+    <t>×0.5</t>
+  </si>
+  <si>
+    <t>×1</t>
+  </si>
+  <si>
+    <t>×2</t>
+  </si>
+  <si>
+    <t>（可以不添加，或者后两行都进行加粗、或者都不进行加粗）</t>
   </si>
 </sst>
 </file>
@@ -459,7 +510,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,31 +537,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -532,6 +568,13 @@
       <b/>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -544,12 +587,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="0" tint="-0.25"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -703,7 +740,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -712,6 +749,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -897,12 +940,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1064,137 +1122,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1204,85 +1262,112 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1596,7 +1681,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="11.1666666666667" customWidth="1"/>
@@ -1608,580 +1693,615 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.15" customHeight="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12" t="s">
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:11">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" ht="15.15" spans="1:11">
-      <c r="A3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="20" t="s">
+      <c r="A3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="25">
         <v>72.7</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="23" t="s">
+    <row r="4" s="14" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="27">
         <v>0.5</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="28">
         <v>78.9</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:11">
-      <c r="A5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="A5" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="21">
         <v>0.5</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="10">
         <v>77.8</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:11">
-      <c r="A6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="A6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="21">
         <v>0.5</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="10">
         <v>77.9</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:11">
-      <c r="A7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="A7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="21">
         <v>0.5</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="10">
         <v>78.7</v>
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:11">
-      <c r="A8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="A8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="21">
         <v>0.5</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="15.15" spans="1:11">
-      <c r="A9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="17" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="21">
         <v>0.5</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="10">
+        <v>79.1</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" spans="1:11">
+      <c r="A10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="10">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" spans="1:11">
+      <c r="A11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="31">
+        <v>1</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="10">
+        <v>79.4</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" spans="1:11">
+      <c r="A12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="10">
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" spans="1:11">
+      <c r="A13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="10">
+        <v>78.1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="31">
+        <v>1</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="10">
+        <v>78.1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="31">
+        <v>1</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="15" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="6">
+      <c r="G16" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="31">
+        <v>1</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="32">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="17" s="15" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A17" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="31">
+        <v>1</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="10">
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="18" s="15" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A18" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="36">
+        <v>1</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="38">
         <v>79.1</v>
-      </c>
-    </row>
-    <row r="10" ht="15.15" spans="1:11">
-      <c r="A10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="6">
-        <v>78.8</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:11">
-      <c r="A11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="27">
-        <v>1</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="6">
-        <v>79.4</v>
-      </c>
-    </row>
-    <row r="12" ht="15.15" spans="1:11">
-      <c r="A12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="6">
-        <v>78.3</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:11">
-      <c r="A13" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="6">
-        <v>78.1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="27">
-        <v>1</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="6">
-        <v>78.1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="27">
-        <v>1</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" s="11" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A16" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="27">
-        <v>1</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" s="11" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A17" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="27">
-        <v>1</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="6">
-        <v>78.3</v>
       </c>
     </row>
   </sheetData>
@@ -2205,238 +2325,228 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="B1:O12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="52.7685185185185" customWidth="1"/>
+    <col min="9" max="9" width="8.12037037037037" customWidth="1"/>
+    <col min="10" max="10" width="10.0648148148148" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.55" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="29.55" customHeight="1" spans="2:15">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.15" spans="1:8">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="2:15">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="15.15" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.789</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.787</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="J8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="J9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="J10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="J11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="J12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="6">
-        <v>0.727</v>
-      </c>
-    </row>
-    <row r="4" ht="15.15" spans="1:8">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0.789</v>
-      </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:8">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.787</v>
-      </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" ht="15.15"/>
-    <row r="10" ht="15.15" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="15.15" spans="1:8">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:8">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="15.15" spans="1:8">
-      <c r="A14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.795</v>
+      <c r="O12" s="1">
+        <v>79.1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="E10:E11"/>
+  <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2447,232 +2557,191 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="14" max="14" width="18.537037037037" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="29.55" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="29.55" customHeight="1" spans="1:14">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.15" spans="1:7">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="15.15" spans="1:14">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="15.15" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="10">
         <v>0.778</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.779</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.787</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="I7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="6">
-        <v>0.779</v>
-      </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.787</v>
-      </c>
-    </row>
-    <row r="9" ht="15.15"/>
-    <row r="10" ht="15.15" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="15.15" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:7">
-      <c r="A13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="15.15" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.795</v>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="I9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="1">
+        <v>79.1</v>
+      </c>
+      <c r="M9" s="12">
+        <v>16.37</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2683,20 +2752,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="B2:E6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1">
+        <v>79.1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
+    <workbookView windowWidth="20820" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="全部数据" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
   <si>
     <t>主干框架的消融</t>
   </si>
@@ -454,25 +454,28 @@
     <t>R7</t>
   </si>
   <si>
+    <t>79.0‘</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>2G-CATH</t>
+  </si>
+  <si>
+    <t>1H-CATH</t>
+  </si>
+  <si>
+    <t>训练时间</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
     <t>？</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>2G-CATH</t>
-  </si>
-  <si>
-    <t>1H-CATH</t>
-  </si>
-  <si>
-    <t>训练时间</t>
-  </si>
-  <si>
-    <t>R4</t>
   </si>
   <si>
     <t>R3</t>
@@ -510,7 +513,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +550,28 @@
       <u/>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1122,137 +1147,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1295,7 +1320,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1319,25 +1353,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1349,7 +1383,7 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1364,7 +1398,7 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1693,153 +1727,153 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.15" customHeight="1" spans="1:11">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="19"/>
+      <c r="E1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:11">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" ht="15.15" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="24" t="s">
+      <c r="A3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="28">
         <v>72.7</v>
       </c>
     </row>
-    <row r="4" s="14" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="27" t="s">
+    <row r="4" s="17" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="30">
         <v>0.5</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="31">
         <v>78.9</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:11">
-      <c r="A5" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="21" t="s">
+      <c r="A5" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="24">
         <v>0.5</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="10" t="s">
@@ -1850,31 +1884,31 @@
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:11">
-      <c r="A6" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="21" t="s">
+      <c r="A6" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="24">
         <v>0.5</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="10" t="s">
@@ -1885,31 +1919,31 @@
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:11">
-      <c r="A7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="21" t="s">
+      <c r="A7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="24">
         <v>0.5</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="10" t="s">
@@ -1920,31 +1954,31 @@
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:11">
-      <c r="A8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="21" t="s">
+      <c r="A8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="24">
         <v>0.5</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="10" t="s">
@@ -1955,31 +1989,31 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="30" t="s">
+      <c r="A9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="24">
         <v>0.5</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="10" t="s">
@@ -1990,31 +2024,31 @@
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:11">
-      <c r="A10" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="21" t="s">
+      <c r="A10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="25">
         <v>0.1</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="10" t="s">
@@ -2025,31 +2059,31 @@
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:11">
-      <c r="A11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="A11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="34">
         <v>1</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="10" t="s">
@@ -2060,31 +2094,31 @@
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:11">
-      <c r="A12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="22" t="s">
+      <c r="A12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="24">
         <v>0.5</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="10" t="s">
@@ -2095,31 +2129,31 @@
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:11">
-      <c r="A13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="21" t="s">
+      <c r="A13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="24" t="s">
         <v>34</v>
       </c>
       <c r="J13" s="10" t="s">
@@ -2130,31 +2164,31 @@
       </c>
     </row>
     <row r="14" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="A14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="34">
         <v>1</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="10" t="s">
@@ -2165,142 +2199,142 @@
       </c>
     </row>
     <row r="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="21" t="s">
+      <c r="A15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="34">
         <v>1</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="35" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" s="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="30" t="s">
+    <row r="16" s="18" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="34">
         <v>1</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="35">
         <v>78.8</v>
       </c>
     </row>
-    <row r="17" s="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A17" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="30" t="s">
+    <row r="17" s="18" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="34">
         <v>1</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="35" t="s">
         <v>41</v>
       </c>
       <c r="K17" s="10">
         <v>78.3</v>
       </c>
     </row>
-    <row r="18" s="15" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A18" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="35" t="s">
+    <row r="18" s="18" customFormat="1" ht="15.15" spans="1:11">
+      <c r="A18" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="39">
         <v>1</v>
       </c>
-      <c r="I18" s="35" t="s">
+      <c r="I18" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="37" t="s">
+      <c r="J18" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="41">
         <v>79.1</v>
       </c>
     </row>
@@ -2441,7 +2475,7 @@
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -2461,27 +2495,27 @@
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="J9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="1" t="s">
+      <c r="J9" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="O9" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:15">
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="15" t="s">
         <v>14</v>
       </c>
       <c r="K10" s="3" t="s">
@@ -2496,12 +2530,12 @@
       <c r="N10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>49</v>
+      <c r="O10" s="1">
+        <v>78.7</v>
       </c>
     </row>
     <row r="11" spans="2:15">
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K11" s="4" t="s">
@@ -2516,12 +2550,12 @@
       <c r="N11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>49</v>
+      <c r="O11" s="1">
+        <v>78.7</v>
       </c>
     </row>
     <row r="12" spans="2:15">
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -2696,7 +2730,7 @@
         <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M7" s="11"/>
     </row>
@@ -2708,10 +2742,10 @@
         <v>13</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
+      </c>
+      <c r="L8" s="1">
+        <v>79.3</v>
       </c>
       <c r="M8" s="11"/>
     </row>
@@ -2732,7 +2766,7 @@
         <v>16.37</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2757,7 +2791,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -2768,29 +2802,29 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -2801,16 +2835,16 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="66">
   <si>
     <t>主干框架的消融</t>
   </si>
@@ -457,10 +457,13 @@
     <t>79.0‘</t>
   </si>
   <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>R5</t>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R8</t>
   </si>
   <si>
     <t>2G-CATH</t>
@@ -472,13 +475,13 @@
     <t>训练时间</t>
   </si>
   <si>
-    <t>R4</t>
+    <t>R10</t>
   </si>
   <si>
     <t>？</t>
   </si>
   <si>
-    <t>R3</t>
+    <t>R9</t>
   </si>
   <si>
     <t>RTX 2080 Ti x2</t>
@@ -2568,7 +2571,7 @@
         <v>14</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="O12" s="1">
         <v>79.1</v>
@@ -2650,7 +2653,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="10">
         <v>0.778</v>
@@ -2673,7 +2676,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" s="10">
         <v>0.779</v>
@@ -2716,7 +2719,7 @@
         <v>8</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2727,10 +2730,10 @@
         <v>13</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7" s="11"/>
     </row>
@@ -2742,7 +2745,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="1">
         <v>79.3</v>
@@ -2757,7 +2760,7 @@
         <v>14</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L9" s="1">
         <v>79.1</v>
@@ -2766,7 +2769,7 @@
         <v>16.37</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +2794,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -2802,29 +2805,29 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -2835,16 +2838,16 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/resultAnalysis.xlsx
+++ b/analysis/resultAnalysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20820" windowHeight="9720" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="全部数据" sheetId="1" r:id="rId1"/>
@@ -119,18 +119,33 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>I2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>I2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>Q5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -138,17 +153,19 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Q5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>Q4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -156,17 +173,19 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Q4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>Q3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -174,17 +193,24 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Q3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>Q2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>79.5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -192,28 +218,39 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Q2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>79.5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>79.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>79.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -221,17 +258,19 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>79.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+      <t>79.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -239,44 +278,9 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>79.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>79.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
@@ -516,7 +520,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -607,9 +611,32 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <u/>
       <sz val="10.5"/>
-      <color theme="1"/>
+      <color rgb="FF7030A0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10.5"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF7030A0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1150,137 +1177,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1368,25 +1395,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1401,7 +1437,7 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1870,19 +1906,19 @@
       <c r="F5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="33">
         <v>0.5</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="34">
         <v>77.8</v>
       </c>
     </row>
@@ -1905,19 +1941,19 @@
       <c r="F6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="33">
         <v>0.5</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="34">
         <v>77.9</v>
       </c>
     </row>
@@ -1940,58 +1976,58 @@
       <c r="F7" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="33">
         <v>0.5</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="34">
         <v>78.7</v>
       </c>
     </row>
     <row r="8" ht="15.15" spans="1:11">
-      <c r="A8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="26" t="s">
+      <c r="A8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="33">
         <v>0.5</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="34" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" ht="15.15" spans="1:11">
       <c r="A9" s="26" t="s">
         <v>14</v>
       </c>
@@ -2007,7 +2043,7 @@
       <c r="E9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="24" t="s">
@@ -2026,7 +2062,7 @@
         <v>79.1</v>
       </c>
     </row>
-    <row r="10" ht="15.15" spans="1:11">
+    <row r="10" ht="15.15" hidden="1" spans="1:11">
       <c r="A10" s="26" t="s">
         <v>14</v>
       </c>
@@ -2042,7 +2078,7 @@
       <c r="E10" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="24" t="s">
@@ -2061,7 +2097,7 @@
         <v>78.8</v>
       </c>
     </row>
-    <row r="11" ht="15.15" spans="1:11">
+    <row r="11" ht="15.15" hidden="1" spans="1:11">
       <c r="A11" s="26" t="s">
         <v>14</v>
       </c>
@@ -2077,13 +2113,13 @@
       <c r="E11" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="37">
         <v>1</v>
       </c>
       <c r="I11" s="24" t="s">
@@ -2096,7 +2132,7 @@
         <v>79.4</v>
       </c>
     </row>
-    <row r="12" ht="15.15" spans="1:11">
+    <row r="12" ht="15.15" hidden="1" spans="1:11">
       <c r="A12" s="26" t="s">
         <v>14</v>
       </c>
@@ -2112,7 +2148,7 @@
       <c r="E12" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="25" t="s">
@@ -2147,13 +2183,13 @@
       <c r="E13" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="37" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="24" t="s">
@@ -2182,13 +2218,13 @@
       <c r="E14" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="37">
         <v>1</v>
       </c>
       <c r="I14" s="24" t="s">
@@ -2217,89 +2253,89 @@
       <c r="E15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="36" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="37">
         <v>1</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" s="18" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="33" t="s">
+      <c r="A16" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="37">
         <v>1</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="38">
         <v>78.8</v>
       </c>
     </row>
     <row r="17" s="18" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="33" t="s">
+      <c r="C17" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>25</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="37">
         <v>1</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="38" t="s">
         <v>41</v>
       </c>
       <c r="K17" s="10">
@@ -2307,37 +2343,37 @@
       </c>
     </row>
     <row r="18" s="18" customFormat="1" ht="15.15" spans="1:11">
-      <c r="A18" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="38" t="s">
+      <c r="A18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="42">
         <v>1</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="40" t="s">
+      <c r="J18" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="K18" s="41">
+      <c r="K18" s="44">
         <v>79.1</v>
       </c>
     </row>
